--- a/t1_confection/A1_Outputs/A1_Outputs_NDC_NoRPO/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_NDC_NoRPO/A-O_AR_Model_Base_Year.xlsx
@@ -9355,7 +9355,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>PWRBIOARGXX</t>
@@ -9379,7 +9378,6 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -9398,7 +9396,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>PWRBIOBOLXX</t>
@@ -9422,7 +9419,6 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9441,7 +9437,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>PWRBIOBRAXX</t>
@@ -9465,7 +9460,6 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9484,7 +9478,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRBIOCHLXX</t>
@@ -9508,7 +9501,6 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9527,7 +9519,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>PWRBIOCOLXX</t>
@@ -9551,7 +9542,6 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9570,7 +9560,6 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>PWRBIOCRIXX</t>
@@ -9594,7 +9583,6 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9613,7 +9601,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>PWRBIODOMXX</t>
@@ -9637,7 +9624,6 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9656,7 +9642,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>PWRBIOECUXX</t>
@@ -9680,7 +9665,6 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9699,7 +9683,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>PWRBIOGTMXX</t>
@@ -9723,7 +9706,6 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9742,7 +9724,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>PWRBIOHNDXX</t>
@@ -9766,7 +9747,6 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9785,7 +9765,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>PWRBIOMEXXX</t>
@@ -9809,7 +9788,6 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9828,7 +9806,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRBIONICXX</t>
@@ -9852,7 +9829,6 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9871,7 +9847,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>PWRBIOPANXX</t>
@@ -9895,7 +9870,6 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9914,7 +9888,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>PWRBIOPERXX</t>
@@ -9938,7 +9911,6 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9957,7 +9929,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>PWRBIOPRYXX</t>
@@ -9981,7 +9952,6 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10000,7 +9970,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>PWRBIOSLVXX</t>
@@ -10024,7 +9993,6 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10043,7 +10011,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>PWRBIOURYXX</t>
@@ -10067,7 +10034,6 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10086,7 +10052,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>PWRCOAARGXX</t>
@@ -10110,7 +10075,6 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10129,7 +10093,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>PWRCOAARGXX</t>
@@ -10153,7 +10116,6 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10172,7 +10134,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRCOABRAXX</t>
@@ -10196,7 +10157,6 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10215,7 +10175,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>PWRCOABRAXX</t>
@@ -10239,7 +10198,6 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10258,7 +10216,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>PWRCOACHLXX</t>
@@ -10282,7 +10239,6 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10301,7 +10257,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>PWRCOACHLXX</t>
@@ -10325,7 +10280,6 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -10344,7 +10298,6 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>PWRCOACOLXX</t>
@@ -10368,7 +10321,6 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -10387,7 +10339,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>PWRCOACOLXX</t>
@@ -10411,7 +10362,6 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -10430,7 +10380,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>PWRCOADOMXX</t>
@@ -10454,7 +10403,6 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -10473,7 +10421,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>PWRCOADOMXX</t>
@@ -10497,7 +10444,6 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -10516,7 +10462,6 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRCOAGTMXX</t>
@@ -10540,7 +10485,6 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -10559,7 +10503,6 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>PWRCOAGTMXX</t>
@@ -10583,7 +10526,6 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -10602,7 +10544,6 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>PWRCOAMEXXX</t>
@@ -10626,7 +10567,6 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -10645,7 +10585,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>PWRCOAMEXXX</t>
@@ -10669,7 +10608,6 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -10688,7 +10626,6 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>PWRCOAPANXX</t>
@@ -10712,7 +10649,6 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -10731,7 +10667,6 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>PWRCOAPANXX</t>
@@ -10755,7 +10690,6 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -10774,7 +10708,6 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>PWRCOAPERXX</t>
@@ -10798,7 +10731,6 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -10817,7 +10749,6 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>PWRCOAPERXX</t>
@@ -10841,7 +10772,6 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -10860,7 +10790,6 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRGEOCHLXX</t>
@@ -10884,7 +10813,6 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -10903,7 +10831,6 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>PWRGEOCRIXX</t>
@@ -10927,7 +10854,6 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -10946,7 +10872,6 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>PWRGEOGTMXX</t>
@@ -10970,7 +10895,6 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -10989,7 +10913,6 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>PWRGEOHNDXX</t>
@@ -11013,7 +10936,6 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -11032,7 +10954,6 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>PWRGEOMEXXX</t>
@@ -11056,7 +10977,6 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -11075,7 +10995,6 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>PWRGEONICXX</t>
@@ -11099,7 +11018,6 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -11118,7 +11036,6 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>PWRGEOSLVXX</t>
@@ -11142,7 +11059,6 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -11161,7 +11077,6 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>PWRHYDARGXX</t>
@@ -11185,7 +11100,6 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -11204,7 +11118,6 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRHYDBOLXX</t>
@@ -11228,7 +11141,6 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -11247,7 +11159,6 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>PWRHYDBRAXX</t>
@@ -11271,7 +11182,6 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -11290,7 +11200,6 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>PWRHYDCHLXX</t>
@@ -11314,7 +11223,6 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -11333,7 +11241,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>PWRHYDCOLXX</t>
@@ -11357,7 +11264,6 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -11376,7 +11282,6 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>PWRHYDCRIXX</t>
@@ -11400,7 +11305,6 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -11419,7 +11323,6 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>PWRHYDDOMXX</t>
@@ -11443,7 +11346,6 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -11462,7 +11364,6 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>PWRHYDECUXX</t>
@@ -11486,7 +11387,6 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -11505,7 +11405,6 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>PWRHYDGTMXX</t>
@@ -11529,7 +11428,6 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -11548,7 +11446,6 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRHYDHNDXX</t>
@@ -11572,7 +11469,6 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -11591,7 +11487,6 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>PWRHYDHTIXX</t>
@@ -11615,7 +11510,6 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -11634,7 +11528,6 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>PWRHYDMEXXX</t>
@@ -11658,7 +11551,6 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -11677,7 +11569,6 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>PWRHYDNICXX</t>
@@ -11701,7 +11592,6 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -11720,7 +11610,6 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>PWRHYDPANXX</t>
@@ -11744,7 +11633,6 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -11763,7 +11651,6 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>PWRHYDPERXX</t>
@@ -11787,7 +11674,6 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -11806,7 +11692,6 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>PWRHYDPRYXX</t>
@@ -11830,7 +11715,6 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -11849,7 +11733,6 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>PWRHYDSLVXX</t>
@@ -11873,7 +11756,6 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -11892,7 +11774,6 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRHYDURYXX</t>
@@ -11916,7 +11797,6 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -11935,7 +11815,6 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>PWRNGSARGXX</t>
@@ -11959,7 +11838,6 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -11978,7 +11856,6 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>PWRNGSARGXX</t>
@@ -12002,7 +11879,6 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -12021,7 +11897,6 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>PWRNGSBOLXX</t>
@@ -12045,7 +11920,6 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -12064,7 +11938,6 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>PWRNGSBOLXX</t>
@@ -12088,7 +11961,6 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -12107,7 +11979,6 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>PWRNGSBRAXX</t>
@@ -12131,7 +12002,6 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -12150,7 +12020,6 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>PWRNGSBRAXX</t>
@@ -12174,7 +12043,6 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -12193,7 +12061,6 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>PWRNGSCHLXX</t>
@@ -12217,7 +12084,6 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -12236,7 +12102,6 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRNGSCHLXX</t>
@@ -12260,7 +12125,6 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -12279,7 +12143,6 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>PWRNGSCOLXX</t>
@@ -12303,7 +12166,6 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -12322,7 +12184,6 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>PWRNGSCOLXX</t>
@@ -12346,7 +12207,6 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -12365,7 +12225,6 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>PWRNGSDOMXX</t>
@@ -12389,7 +12248,6 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -12408,7 +12266,6 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>PWRNGSDOMXX</t>
@@ -12432,7 +12289,6 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -12451,7 +12307,6 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>PWRNGSECUXX</t>
@@ -12475,7 +12330,6 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -12494,7 +12348,6 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>PWRNGSECUXX</t>
@@ -12518,7 +12371,6 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -12537,7 +12389,6 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>PWRNGSGTMXX</t>
@@ -12561,7 +12412,6 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -12580,7 +12430,6 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWRNGSGTMXX</t>
@@ -12604,7 +12453,6 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -12623,7 +12471,6 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>PWRNGSMEXXX</t>
@@ -12647,7 +12494,6 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12666,7 +12512,6 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>PWRNGSMEXXX</t>
@@ -12690,7 +12535,6 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -12709,7 +12553,6 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>PWRNGSPANXX</t>
@@ -12733,7 +12576,6 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12752,7 +12594,6 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>PWRNGSPANXX</t>
@@ -12776,7 +12617,6 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12795,7 +12635,6 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>PWRNGSPERXX</t>
@@ -12819,7 +12658,6 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12838,7 +12676,6 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>PWRNGSPERXX</t>
@@ -12862,7 +12699,6 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12881,7 +12717,6 @@
       <c r="D84" t="n">
         <v>1</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>PWRNGSSLVXX</t>
@@ -12905,7 +12740,6 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12924,7 +12758,6 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>PWRNGSSLVXX</t>
@@ -12948,7 +12781,6 @@
       <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12967,7 +12799,6 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>PWROILARGXX</t>
@@ -12991,7 +12822,6 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -13010,7 +12840,6 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>PWROILARGXX</t>
@@ -13034,7 +12863,6 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13053,7 +12881,6 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>PWROILBOLXX</t>
@@ -13077,7 +12904,6 @@
       <c r="J88" t="n">
         <v>1</v>
       </c>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13096,7 +12922,6 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>PWROILBOLXX</t>
@@ -13120,7 +12945,6 @@
       <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13139,7 +12963,6 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>PWROILBRAXX</t>
@@ -13163,7 +12986,6 @@
       <c r="J90" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13182,7 +13004,6 @@
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>PWROILBRAXX</t>
@@ -13206,7 +13027,6 @@
       <c r="J91" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13225,7 +13045,6 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>PWROILBRBXX</t>
@@ -13249,7 +13068,6 @@
       <c r="J92" t="n">
         <v>1</v>
       </c>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -13268,7 +13086,6 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>PWROILBRBXX</t>
@@ -13292,7 +13109,6 @@
       <c r="J93" t="n">
         <v>1</v>
       </c>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13311,7 +13127,6 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>PWROILCHLXX</t>
@@ -13335,7 +13150,6 @@
       <c r="J94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13354,7 +13168,6 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>PWROILCHLXX</t>
@@ -13378,7 +13191,6 @@
       <c r="J95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13397,7 +13209,6 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>PWROILCOLXX</t>
@@ -13421,7 +13232,6 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
-      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13440,7 +13250,6 @@
       <c r="D97" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>PWROILCOLXX</t>
@@ -13464,7 +13273,6 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13483,7 +13291,6 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>PWROILCRIXX</t>
@@ -13507,7 +13314,6 @@
       <c r="J98" t="n">
         <v>1</v>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13526,7 +13332,6 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>PWROILCRIXX</t>
@@ -13550,7 +13355,6 @@
       <c r="J99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13569,7 +13373,6 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>PWROILDOMXX</t>
@@ -13593,7 +13396,6 @@
       <c r="J100" t="n">
         <v>1</v>
       </c>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13612,7 +13414,6 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>PWROILDOMXX</t>
@@ -13636,7 +13437,6 @@
       <c r="J101" t="n">
         <v>1</v>
       </c>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13655,7 +13455,6 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>PWROILECUXX</t>
@@ -13679,7 +13478,6 @@
       <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13698,7 +13496,6 @@
       <c r="D103" t="n">
         <v>1</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>PWROILECUXX</t>
@@ -13722,7 +13519,6 @@
       <c r="J103" t="n">
         <v>1</v>
       </c>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13741,7 +13537,6 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>PWROILGTMXX</t>
@@ -13765,7 +13560,6 @@
       <c r="J104" t="n">
         <v>1</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13784,7 +13578,6 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>PWROILGTMXX</t>
@@ -13808,7 +13601,6 @@
       <c r="J105" t="n">
         <v>1</v>
       </c>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13827,7 +13619,6 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>PWROILHNDXX</t>
@@ -13851,7 +13642,6 @@
       <c r="J106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13870,7 +13660,6 @@
       <c r="D107" t="n">
         <v>1</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>PWROILHNDXX</t>
@@ -13894,7 +13683,6 @@
       <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13913,7 +13701,6 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>PWROILHTIXX</t>
@@ -13937,7 +13724,6 @@
       <c r="J108" t="n">
         <v>1</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13956,7 +13742,6 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>PWROILHTIXX</t>
@@ -13980,7 +13765,6 @@
       <c r="J109" t="n">
         <v>1</v>
       </c>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13999,7 +13783,6 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>PWROILMEXXX</t>
@@ -14023,7 +13806,6 @@
       <c r="J110" t="n">
         <v>1</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14042,7 +13824,6 @@
       <c r="D111" t="n">
         <v>1</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>PWROILMEXXX</t>
@@ -14066,7 +13847,6 @@
       <c r="J111" t="n">
         <v>1</v>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14085,7 +13865,6 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>PWROILNICXX</t>
@@ -14109,7 +13888,6 @@
       <c r="J112" t="n">
         <v>1</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14128,7 +13906,6 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>PWROILNICXX</t>
@@ -14152,7 +13929,6 @@
       <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14171,7 +13947,6 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>PWROILPANXX</t>
@@ -14195,7 +13970,6 @@
       <c r="J114" t="n">
         <v>1</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14214,7 +13988,6 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>PWROILPANXX</t>
@@ -14238,7 +14011,6 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14257,7 +14029,6 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>PWROILPERXX</t>
@@ -14281,7 +14052,6 @@
       <c r="J116" t="n">
         <v>1</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14300,7 +14070,6 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>PWROILPERXX</t>
@@ -14324,7 +14093,6 @@
       <c r="J117" t="n">
         <v>1</v>
       </c>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14343,7 +14111,6 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>PWROILPRYXX</t>
@@ -14367,7 +14134,6 @@
       <c r="J118" t="n">
         <v>1</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14386,7 +14152,6 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>PWROILPRYXX</t>
@@ -14410,7 +14175,6 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14429,7 +14193,6 @@
       <c r="D120" t="n">
         <v>1</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>PWROILSLVXX</t>
@@ -14453,7 +14216,6 @@
       <c r="J120" t="n">
         <v>1</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14472,7 +14234,6 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>PWROILSLVXX</t>
@@ -14496,7 +14257,6 @@
       <c r="J121" t="n">
         <v>1</v>
       </c>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14515,7 +14275,6 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>PWROILURYXX</t>
@@ -14539,7 +14298,6 @@
       <c r="J122" t="n">
         <v>1</v>
       </c>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14558,7 +14316,6 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>PWROILURYXX</t>
@@ -14582,7 +14339,6 @@
       <c r="J123" t="n">
         <v>1</v>
       </c>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14601,7 +14357,6 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>PWRPETARGXX</t>
@@ -14625,7 +14380,6 @@
       <c r="J124" t="n">
         <v>1</v>
       </c>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14644,7 +14398,6 @@
       <c r="D125" t="n">
         <v>1</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>PWRPETARGXX</t>
@@ -14668,7 +14421,6 @@
       <c r="J125" t="n">
         <v>1</v>
       </c>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14687,7 +14439,6 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>PWRPETBOLXX</t>
@@ -14711,7 +14462,6 @@
       <c r="J126" t="n">
         <v>1</v>
       </c>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14730,7 +14480,6 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>PWRPETBOLXX</t>
@@ -14754,7 +14503,6 @@
       <c r="J127" t="n">
         <v>1</v>
       </c>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14773,7 +14521,6 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>PWRPETBRAXX</t>
@@ -14797,7 +14544,6 @@
       <c r="J128" t="n">
         <v>1</v>
       </c>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14816,7 +14562,6 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>PWRPETBRAXX</t>
@@ -14840,7 +14585,6 @@
       <c r="J129" t="n">
         <v>1</v>
       </c>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14859,7 +14603,6 @@
       <c r="D130" t="n">
         <v>1</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>PWRPETBRBXX</t>
@@ -14883,7 +14626,6 @@
       <c r="J130" t="n">
         <v>1</v>
       </c>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14902,7 +14644,6 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>PWRPETBRBXX</t>
@@ -14926,7 +14667,6 @@
       <c r="J131" t="n">
         <v>1</v>
       </c>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14945,7 +14685,6 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>PWRPETCHLXX</t>
@@ -14969,7 +14708,6 @@
       <c r="J132" t="n">
         <v>1</v>
       </c>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14988,7 +14726,6 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>PWRPETCHLXX</t>
@@ -15012,7 +14749,6 @@
       <c r="J133" t="n">
         <v>1</v>
       </c>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15031,7 +14767,6 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>PWRPETCOLXX</t>
@@ -15055,7 +14790,6 @@
       <c r="J134" t="n">
         <v>1</v>
       </c>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15074,7 +14808,6 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>PWRPETCOLXX</t>
@@ -15098,7 +14831,6 @@
       <c r="J135" t="n">
         <v>1</v>
       </c>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15117,7 +14849,6 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>PWRPETCRIXX</t>
@@ -15141,7 +14872,6 @@
       <c r="J136" t="n">
         <v>1</v>
       </c>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15160,7 +14890,6 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>PWRPETCRIXX</t>
@@ -15184,7 +14913,6 @@
       <c r="J137" t="n">
         <v>1</v>
       </c>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15203,7 +14931,6 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>PWRPETDOMXX</t>
@@ -15227,7 +14954,6 @@
       <c r="J138" t="n">
         <v>1</v>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15246,7 +14972,6 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>PWRPETDOMXX</t>
@@ -15270,7 +14995,6 @@
       <c r="J139" t="n">
         <v>1</v>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15289,7 +15013,6 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>PWRPETECUXX</t>
@@ -15313,7 +15036,6 @@
       <c r="J140" t="n">
         <v>1</v>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15332,7 +15054,6 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>PWRPETECUXX</t>
@@ -15356,7 +15077,6 @@
       <c r="J141" t="n">
         <v>1</v>
       </c>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15375,7 +15095,6 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>PWRPETGTMXX</t>
@@ -15399,7 +15118,6 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15418,7 +15136,6 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>PWRPETGTMXX</t>
@@ -15442,7 +15159,6 @@
       <c r="J143" t="n">
         <v>1</v>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15461,7 +15177,6 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>PWRPETHNDXX</t>
@@ -15485,7 +15200,6 @@
       <c r="J144" t="n">
         <v>1</v>
       </c>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15504,7 +15218,6 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>PWRPETHNDXX</t>
@@ -15528,7 +15241,6 @@
       <c r="J145" t="n">
         <v>1</v>
       </c>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15547,7 +15259,6 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>PWRPETHTIXX</t>
@@ -15571,7 +15282,6 @@
       <c r="J146" t="n">
         <v>1</v>
       </c>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15590,7 +15300,6 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>PWRPETHTIXX</t>
@@ -15614,7 +15323,6 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15633,7 +15341,6 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>PWRPETMEXXX</t>
@@ -15657,7 +15364,6 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15676,7 +15382,6 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>PWRPETMEXXX</t>
@@ -15700,7 +15405,6 @@
       <c r="J149" t="n">
         <v>1</v>
       </c>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15719,7 +15423,6 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>PWRPETNICXX</t>
@@ -15743,7 +15446,6 @@
       <c r="J150" t="n">
         <v>1</v>
       </c>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15762,7 +15464,6 @@
       <c r="D151" t="n">
         <v>1</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>PWRPETNICXX</t>
@@ -15786,7 +15487,6 @@
       <c r="J151" t="n">
         <v>1</v>
       </c>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15805,7 +15505,6 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>PWRPETPANXX</t>
@@ -15829,7 +15528,6 @@
       <c r="J152" t="n">
         <v>1</v>
       </c>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15848,7 +15546,6 @@
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>PWRPETPANXX</t>
@@ -15872,7 +15569,6 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15891,7 +15587,6 @@
       <c r="D154" t="n">
         <v>1</v>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>PWRPETPERXX</t>
@@ -15915,7 +15610,6 @@
       <c r="J154" t="n">
         <v>1</v>
       </c>
-      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15934,7 +15628,6 @@
       <c r="D155" t="n">
         <v>1</v>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>PWRPETPERXX</t>
@@ -15958,7 +15651,6 @@
       <c r="J155" t="n">
         <v>1</v>
       </c>
-      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15977,7 +15669,6 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>PWRPETPRYXX</t>
@@ -16001,7 +15692,6 @@
       <c r="J156" t="n">
         <v>1</v>
       </c>
-      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16020,7 +15710,6 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>PWRPETPRYXX</t>
@@ -16044,7 +15733,6 @@
       <c r="J157" t="n">
         <v>1</v>
       </c>
-      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16063,7 +15751,6 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>PWRPETSLVXX</t>
@@ -16087,7 +15774,6 @@
       <c r="J158" t="n">
         <v>1</v>
       </c>
-      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16106,7 +15792,6 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>PWRPETSLVXX</t>
@@ -16130,7 +15815,6 @@
       <c r="J159" t="n">
         <v>1</v>
       </c>
-      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16149,7 +15833,6 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>PWRPETURYXX</t>
@@ -16173,7 +15856,6 @@
       <c r="J160" t="n">
         <v>1</v>
       </c>
-      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16192,7 +15874,6 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>PWRPETURYXX</t>
@@ -16216,7 +15897,6 @@
       <c r="J161" t="n">
         <v>1</v>
       </c>
-      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16235,7 +15915,6 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>PWRSPVARGXX</t>
@@ -16259,7 +15938,6 @@
       <c r="J162" t="n">
         <v>1</v>
       </c>
-      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16278,7 +15956,6 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>PWRSPVBOLXX</t>
@@ -16302,7 +15979,6 @@
       <c r="J163" t="n">
         <v>1</v>
       </c>
-      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16321,7 +15997,6 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>PWRSPVBRAXX</t>
@@ -16345,7 +16020,6 @@
       <c r="J164" t="n">
         <v>1</v>
       </c>
-      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16364,7 +16038,6 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>PWRSPVBRBXX</t>
@@ -16388,7 +16061,6 @@
       <c r="J165" t="n">
         <v>1</v>
       </c>
-      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16407,7 +16079,6 @@
       <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>PWRSPVCHLXX</t>
@@ -16431,7 +16102,6 @@
       <c r="J166" t="n">
         <v>1</v>
       </c>
-      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16450,7 +16120,6 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>PWRSPVCOLXX</t>
@@ -16474,7 +16143,6 @@
       <c r="J167" t="n">
         <v>1</v>
       </c>
-      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16493,7 +16161,6 @@
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>PWRSPVCRIXX</t>
@@ -16517,7 +16184,6 @@
       <c r="J168" t="n">
         <v>1</v>
       </c>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -16536,7 +16202,6 @@
       <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>PWRSPVDOMXX</t>
@@ -16560,7 +16225,6 @@
       <c r="J169" t="n">
         <v>1</v>
       </c>
-      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -16579,7 +16243,6 @@
       <c r="D170" t="n">
         <v>1</v>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>PWRSPVECUXX</t>
@@ -16603,7 +16266,6 @@
       <c r="J170" t="n">
         <v>1</v>
       </c>
-      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -16622,7 +16284,6 @@
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>PWRSPVGTMXX</t>
@@ -16646,7 +16307,6 @@
       <c r="J171" t="n">
         <v>1</v>
       </c>
-      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -16665,7 +16325,6 @@
       <c r="D172" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>PWRSPVHNDXX</t>
@@ -16689,7 +16348,6 @@
       <c r="J172" t="n">
         <v>1</v>
       </c>
-      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -16708,7 +16366,6 @@
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>PWRSPVHTIXX</t>
@@ -16732,7 +16389,6 @@
       <c r="J173" t="n">
         <v>1</v>
       </c>
-      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -16751,7 +16407,6 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>PWRSPVMEXXX</t>
@@ -16775,7 +16430,6 @@
       <c r="J174" t="n">
         <v>1</v>
       </c>
-      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -16794,7 +16448,6 @@
       <c r="D175" t="n">
         <v>1</v>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>PWRSPVNICXX</t>
@@ -16818,7 +16471,6 @@
       <c r="J175" t="n">
         <v>1</v>
       </c>
-      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -16837,7 +16489,6 @@
       <c r="D176" t="n">
         <v>1</v>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>PWRSPVPANXX</t>
@@ -16861,7 +16512,6 @@
       <c r="J176" t="n">
         <v>1</v>
       </c>
-      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -16880,7 +16530,6 @@
       <c r="D177" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>PWRSPVPERXX</t>
@@ -16904,7 +16553,6 @@
       <c r="J177" t="n">
         <v>1</v>
       </c>
-      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -16923,7 +16571,6 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>PWRSPVPRYXX</t>
@@ -16947,7 +16594,6 @@
       <c r="J178" t="n">
         <v>1</v>
       </c>
-      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -16966,7 +16612,6 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>PWRSPVSLVXX</t>
@@ -16990,7 +16635,6 @@
       <c r="J179" t="n">
         <v>1</v>
       </c>
-      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -17009,7 +16653,6 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>PWRSPVURYXX</t>
@@ -17033,7 +16676,6 @@
       <c r="J180" t="n">
         <v>1</v>
       </c>
-      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -17052,7 +16694,6 @@
       <c r="D181" t="n">
         <v>1</v>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>PWRURNARGXX</t>
@@ -17076,7 +16717,6 @@
       <c r="J181" t="n">
         <v>1</v>
       </c>
-      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -17095,7 +16735,6 @@
       <c r="D182" t="n">
         <v>1</v>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>PWRURNARGXX</t>
@@ -17119,7 +16758,6 @@
       <c r="J182" t="n">
         <v>1</v>
       </c>
-      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -17138,7 +16776,6 @@
       <c r="D183" t="n">
         <v>1</v>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>PWRURNBRAXX</t>
@@ -17162,7 +16799,6 @@
       <c r="J183" t="n">
         <v>1</v>
       </c>
-      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -17181,7 +16817,6 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>PWRURNBRAXX</t>
@@ -17205,7 +16840,6 @@
       <c r="J184" t="n">
         <v>1</v>
       </c>
-      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -17224,7 +16858,6 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>PWRURNMEXXX</t>
@@ -17248,7 +16881,6 @@
       <c r="J185" t="n">
         <v>1</v>
       </c>
-      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -17267,7 +16899,6 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>PWRURNMEXXX</t>
@@ -17291,7 +16922,6 @@
       <c r="J186" t="n">
         <v>1</v>
       </c>
-      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -17310,7 +16940,6 @@
       <c r="D187" t="n">
         <v>1</v>
       </c>
-      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>PWRWASARGXX</t>
@@ -17334,7 +16963,6 @@
       <c r="J187" t="n">
         <v>1</v>
       </c>
-      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -17353,7 +16981,6 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>PWRWASBOLXX</t>
@@ -17377,7 +17004,6 @@
       <c r="J188" t="n">
         <v>1</v>
       </c>
-      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -17396,7 +17022,6 @@
       <c r="D189" t="n">
         <v>1</v>
       </c>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>PWRWASBRAXX</t>
@@ -17420,7 +17045,6 @@
       <c r="J189" t="n">
         <v>1</v>
       </c>
-      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -17439,7 +17063,6 @@
       <c r="D190" t="n">
         <v>1</v>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>PWRWASBRBXX</t>
@@ -17463,7 +17086,6 @@
       <c r="J190" t="n">
         <v>1</v>
       </c>
-      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -17482,7 +17104,6 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>PWRWASCHLXX</t>
@@ -17506,7 +17127,6 @@
       <c r="J191" t="n">
         <v>1</v>
       </c>
-      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -17525,7 +17145,6 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>PWRWASCOLXX</t>
@@ -17549,7 +17168,6 @@
       <c r="J192" t="n">
         <v>1</v>
       </c>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -17568,7 +17186,6 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>PWRWASCRIXX</t>
@@ -17592,7 +17209,6 @@
       <c r="J193" t="n">
         <v>1</v>
       </c>
-      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -17611,7 +17227,6 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>PWRWASDOMXX</t>
@@ -17635,7 +17250,6 @@
       <c r="J194" t="n">
         <v>1</v>
       </c>
-      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -17654,7 +17268,6 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>PWRWASECUXX</t>
@@ -17678,7 +17291,6 @@
       <c r="J195" t="n">
         <v>1</v>
       </c>
-      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -17697,7 +17309,6 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>PWRWASGTMXX</t>
@@ -17721,7 +17332,6 @@
       <c r="J196" t="n">
         <v>1</v>
       </c>
-      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -17740,7 +17350,6 @@
       <c r="D197" t="n">
         <v>1</v>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>PWRWASHNDXX</t>
@@ -17764,7 +17373,6 @@
       <c r="J197" t="n">
         <v>1</v>
       </c>
-      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -17783,7 +17391,6 @@
       <c r="D198" t="n">
         <v>1</v>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>PWRWASHTIXX</t>
@@ -17807,7 +17414,6 @@
       <c r="J198" t="n">
         <v>1</v>
       </c>
-      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -17826,7 +17432,6 @@
       <c r="D199" t="n">
         <v>1</v>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>PWRWASMEXXX</t>
@@ -17850,7 +17455,6 @@
       <c r="J199" t="n">
         <v>1</v>
       </c>
-      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -17869,7 +17473,6 @@
       <c r="D200" t="n">
         <v>1</v>
       </c>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>PWRWASNICXX</t>
@@ -17893,7 +17496,6 @@
       <c r="J200" t="n">
         <v>1</v>
       </c>
-      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -17912,7 +17514,6 @@
       <c r="D201" t="n">
         <v>1</v>
       </c>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>PWRWASPANXX</t>
@@ -17936,7 +17537,6 @@
       <c r="J201" t="n">
         <v>1</v>
       </c>
-      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -17955,7 +17555,6 @@
       <c r="D202" t="n">
         <v>1</v>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>PWRWASPERXX</t>
@@ -17979,7 +17578,6 @@
       <c r="J202" t="n">
         <v>1</v>
       </c>
-      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -17998,7 +17596,6 @@
       <c r="D203" t="n">
         <v>1</v>
       </c>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>PWRWASPRYXX</t>
@@ -18022,7 +17619,6 @@
       <c r="J203" t="n">
         <v>1</v>
       </c>
-      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -18041,7 +17637,6 @@
       <c r="D204" t="n">
         <v>1</v>
       </c>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>PWRWASSLVXX</t>
@@ -18065,7 +17660,6 @@
       <c r="J204" t="n">
         <v>1</v>
       </c>
-      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -18084,7 +17678,6 @@
       <c r="D205" t="n">
         <v>1</v>
       </c>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>PWRWASURYXX</t>
@@ -18108,7 +17701,6 @@
       <c r="J205" t="n">
         <v>1</v>
       </c>
-      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -18127,7 +17719,6 @@
       <c r="D206" t="n">
         <v>1</v>
       </c>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>PWRWOFARGXX</t>
@@ -18151,7 +17742,6 @@
       <c r="J206" t="n">
         <v>1</v>
       </c>
-      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -18170,7 +17760,6 @@
       <c r="D207" t="n">
         <v>1</v>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>PWRWOFBOLXX</t>
@@ -18194,7 +17783,6 @@
       <c r="J207" t="n">
         <v>1</v>
       </c>
-      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -18213,7 +17801,6 @@
       <c r="D208" t="n">
         <v>1</v>
       </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>PWRWOFBRAXX</t>
@@ -18237,7 +17824,6 @@
       <c r="J208" t="n">
         <v>1</v>
       </c>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -18256,7 +17842,6 @@
       <c r="D209" t="n">
         <v>1</v>
       </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>PWRWOFBRBXX</t>
@@ -18280,7 +17865,6 @@
       <c r="J209" t="n">
         <v>1</v>
       </c>
-      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -18299,7 +17883,6 @@
       <c r="D210" t="n">
         <v>1</v>
       </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>PWRWOFCHLXX</t>
@@ -18323,7 +17906,6 @@
       <c r="J210" t="n">
         <v>1</v>
       </c>
-      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -18342,7 +17924,6 @@
       <c r="D211" t="n">
         <v>1</v>
       </c>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>PWRWOFCOLXX</t>
@@ -18366,7 +17947,6 @@
       <c r="J211" t="n">
         <v>1</v>
       </c>
-      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -18385,7 +17965,6 @@
       <c r="D212" t="n">
         <v>1</v>
       </c>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>PWRWOFCRIXX</t>
@@ -18409,7 +17988,6 @@
       <c r="J212" t="n">
         <v>1</v>
       </c>
-      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -18428,7 +18006,6 @@
       <c r="D213" t="n">
         <v>1</v>
       </c>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>PWRWOFDOMXX</t>
@@ -18452,7 +18029,6 @@
       <c r="J213" t="n">
         <v>1</v>
       </c>
-      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -18471,7 +18047,6 @@
       <c r="D214" t="n">
         <v>1</v>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>PWRWOFECUXX</t>
@@ -18495,7 +18070,6 @@
       <c r="J214" t="n">
         <v>1</v>
       </c>
-      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -18514,7 +18088,6 @@
       <c r="D215" t="n">
         <v>1</v>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>PWRWOFGTMXX</t>
@@ -18538,7 +18111,6 @@
       <c r="J215" t="n">
         <v>1</v>
       </c>
-      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -18557,7 +18129,6 @@
       <c r="D216" t="n">
         <v>1</v>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>PWRWOFHNDXX</t>
@@ -18581,7 +18152,6 @@
       <c r="J216" t="n">
         <v>1</v>
       </c>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -18600,7 +18170,6 @@
       <c r="D217" t="n">
         <v>1</v>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>PWRWOFHTIXX</t>
@@ -18624,7 +18193,6 @@
       <c r="J217" t="n">
         <v>1</v>
       </c>
-      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -18643,7 +18211,6 @@
       <c r="D218" t="n">
         <v>1</v>
       </c>
-      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>PWRWOFMEXXX</t>
@@ -18667,7 +18234,6 @@
       <c r="J218" t="n">
         <v>1</v>
       </c>
-      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -18686,7 +18252,6 @@
       <c r="D219" t="n">
         <v>1</v>
       </c>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>PWRWOFNICXX</t>
@@ -18710,7 +18275,6 @@
       <c r="J219" t="n">
         <v>1</v>
       </c>
-      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -18729,7 +18293,6 @@
       <c r="D220" t="n">
         <v>1</v>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>PWRWOFPANXX</t>
@@ -18753,7 +18316,6 @@
       <c r="J220" t="n">
         <v>1</v>
       </c>
-      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -18772,7 +18334,6 @@
       <c r="D221" t="n">
         <v>1</v>
       </c>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>PWRWOFPERXX</t>
@@ -18796,7 +18357,6 @@
       <c r="J221" t="n">
         <v>1</v>
       </c>
-      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -18815,7 +18375,6 @@
       <c r="D222" t="n">
         <v>1</v>
       </c>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>PWRWOFPRYXX</t>
@@ -18839,7 +18398,6 @@
       <c r="J222" t="n">
         <v>1</v>
       </c>
-      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -18858,7 +18416,6 @@
       <c r="D223" t="n">
         <v>1</v>
       </c>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>PWRWOFSLVXX</t>
@@ -18882,7 +18439,6 @@
       <c r="J223" t="n">
         <v>1</v>
       </c>
-      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -18901,7 +18457,6 @@
       <c r="D224" t="n">
         <v>1</v>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>PWRWOFURYXX</t>
@@ -18925,7 +18480,6 @@
       <c r="J224" t="n">
         <v>1</v>
       </c>
-      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -18944,7 +18498,6 @@
       <c r="D225" t="n">
         <v>1</v>
       </c>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>PWRWONARGXX</t>
@@ -18968,7 +18521,6 @@
       <c r="J225" t="n">
         <v>1</v>
       </c>
-      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -18987,7 +18539,6 @@
       <c r="D226" t="n">
         <v>1</v>
       </c>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>PWRWONBOLXX</t>
@@ -19011,7 +18562,6 @@
       <c r="J226" t="n">
         <v>1</v>
       </c>
-      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -19030,7 +18580,6 @@
       <c r="D227" t="n">
         <v>1</v>
       </c>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>PWRWONBRAXX</t>
@@ -19054,7 +18603,6 @@
       <c r="J227" t="n">
         <v>1</v>
       </c>
-      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -19073,7 +18621,6 @@
       <c r="D228" t="n">
         <v>1</v>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>PWRWONCHLXX</t>
@@ -19097,7 +18644,6 @@
       <c r="J228" t="n">
         <v>1</v>
       </c>
-      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -19116,7 +18662,6 @@
       <c r="D229" t="n">
         <v>1</v>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>PWRWONCOLXX</t>
@@ -19140,7 +18685,6 @@
       <c r="J229" t="n">
         <v>1</v>
       </c>
-      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -19159,7 +18703,6 @@
       <c r="D230" t="n">
         <v>1</v>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>PWRWONCRIXX</t>
@@ -19183,7 +18726,6 @@
       <c r="J230" t="n">
         <v>1</v>
       </c>
-      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -19202,7 +18744,6 @@
       <c r="D231" t="n">
         <v>1</v>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>PWRWONDOMXX</t>
@@ -19226,7 +18767,6 @@
       <c r="J231" t="n">
         <v>1</v>
       </c>
-      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -19245,7 +18785,6 @@
       <c r="D232" t="n">
         <v>1</v>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>PWRWONECUXX</t>
@@ -19269,7 +18808,6 @@
       <c r="J232" t="n">
         <v>1</v>
       </c>
-      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -19288,7 +18826,6 @@
       <c r="D233" t="n">
         <v>1</v>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>PWRWONGTMXX</t>
@@ -19312,7 +18849,6 @@
       <c r="J233" t="n">
         <v>1</v>
       </c>
-      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -19331,7 +18867,6 @@
       <c r="D234" t="n">
         <v>1</v>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>PWRWONHNDXX</t>
@@ -19355,7 +18890,6 @@
       <c r="J234" t="n">
         <v>1</v>
       </c>
-      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -19374,7 +18908,6 @@
       <c r="D235" t="n">
         <v>1</v>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>PWRWONHTIXX</t>
@@ -19398,7 +18931,6 @@
       <c r="J235" t="n">
         <v>1</v>
       </c>
-      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -19417,7 +18949,6 @@
       <c r="D236" t="n">
         <v>1</v>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>PWRWONMEXXX</t>
@@ -19441,7 +18972,6 @@
       <c r="J236" t="n">
         <v>1</v>
       </c>
-      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -19460,7 +18990,6 @@
       <c r="D237" t="n">
         <v>1</v>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>PWRWONNICXX</t>
@@ -19484,7 +19013,6 @@
       <c r="J237" t="n">
         <v>1</v>
       </c>
-      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -19503,7 +19031,6 @@
       <c r="D238" t="n">
         <v>1</v>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>PWRWONPANXX</t>
@@ -19527,7 +19054,6 @@
       <c r="J238" t="n">
         <v>1</v>
       </c>
-      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -19546,7 +19072,6 @@
       <c r="D239" t="n">
         <v>1</v>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>PWRWONPERXX</t>
@@ -19570,7 +19095,6 @@
       <c r="J239" t="n">
         <v>1</v>
       </c>
-      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -19589,7 +19113,6 @@
       <c r="D240" t="n">
         <v>1</v>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>PWRWONPRYXX</t>
@@ -19613,7 +19136,6 @@
       <c r="J240" t="n">
         <v>1</v>
       </c>
-      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -19632,7 +19154,6 @@
       <c r="D241" t="n">
         <v>1</v>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>PWRWONSLVXX</t>
@@ -19656,7 +19177,6 @@
       <c r="J241" t="n">
         <v>1</v>
       </c>
-      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -19675,7 +19195,6 @@
       <c r="D242" t="n">
         <v>1</v>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>PWRWONURYXX</t>
@@ -19699,7 +19218,6 @@
       <c r="J242" t="n">
         <v>1</v>
       </c>
-      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -19718,7 +19236,6 @@
       <c r="D243" t="n">
         <v>1</v>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>TRNARGXXBOLXX</t>
@@ -19742,7 +19259,6 @@
       <c r="J243" t="n">
         <v>1</v>
       </c>
-      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -19761,7 +19277,6 @@
       <c r="D244" t="n">
         <v>1</v>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>TRNARGXXBOLXX</t>
@@ -19785,7 +19300,6 @@
       <c r="J244" t="n">
         <v>1</v>
       </c>
-      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -19804,7 +19318,6 @@
       <c r="D245" t="n">
         <v>1</v>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>TRNARGXXBRAXX</t>
@@ -19828,7 +19341,6 @@
       <c r="J245" t="n">
         <v>1</v>
       </c>
-      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -19847,7 +19359,6 @@
       <c r="D246" t="n">
         <v>1</v>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>TRNARGXXBRAXX</t>
@@ -19871,7 +19382,6 @@
       <c r="J246" t="n">
         <v>1</v>
       </c>
-      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -19890,7 +19400,6 @@
       <c r="D247" t="n">
         <v>1</v>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>TRNARGXXCHLXX</t>
@@ -19914,7 +19423,6 @@
       <c r="J247" t="n">
         <v>1</v>
       </c>
-      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -19933,7 +19441,6 @@
       <c r="D248" t="n">
         <v>1</v>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>TRNARGXXCHLXX</t>
@@ -19957,7 +19464,6 @@
       <c r="J248" t="n">
         <v>1</v>
       </c>
-      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -19976,7 +19482,6 @@
       <c r="D249" t="n">
         <v>1</v>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>TRNARGXXPRYXX</t>
@@ -20000,7 +19505,6 @@
       <c r="J249" t="n">
         <v>1</v>
       </c>
-      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -20019,7 +19523,6 @@
       <c r="D250" t="n">
         <v>1</v>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>TRNARGXXPRYXX</t>
@@ -20043,7 +19546,6 @@
       <c r="J250" t="n">
         <v>1</v>
       </c>
-      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -20062,7 +19564,6 @@
       <c r="D251" t="n">
         <v>1</v>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>TRNARGXXURYXX</t>
@@ -20086,7 +19587,6 @@
       <c r="J251" t="n">
         <v>1</v>
       </c>
-      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -20105,7 +19605,6 @@
       <c r="D252" t="n">
         <v>1</v>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>TRNARGXXURYXX</t>
@@ -20129,7 +19628,6 @@
       <c r="J252" t="n">
         <v>1</v>
       </c>
-      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -20148,7 +19646,6 @@
       <c r="D253" t="n">
         <v>1</v>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>TRNBOLXXBRAXX</t>
@@ -20172,7 +19669,6 @@
       <c r="J253" t="n">
         <v>1</v>
       </c>
-      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -20191,7 +19687,6 @@
       <c r="D254" t="n">
         <v>1</v>
       </c>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>TRNBOLXXBRAXX</t>
@@ -20215,7 +19710,6 @@
       <c r="J254" t="n">
         <v>1</v>
       </c>
-      <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -20234,7 +19728,6 @@
       <c r="D255" t="n">
         <v>1</v>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>TRNBOLXXCHLXX</t>
@@ -20258,7 +19751,6 @@
       <c r="J255" t="n">
         <v>1</v>
       </c>
-      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -20277,7 +19769,6 @@
       <c r="D256" t="n">
         <v>1</v>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>TRNBOLXXCHLXX</t>
@@ -20301,7 +19792,6 @@
       <c r="J256" t="n">
         <v>1</v>
       </c>
-      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -20320,7 +19810,6 @@
       <c r="D257" t="n">
         <v>1</v>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>TRNBOLXXPERXX</t>
@@ -20344,7 +19833,6 @@
       <c r="J257" t="n">
         <v>1</v>
       </c>
-      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -20363,7 +19851,6 @@
       <c r="D258" t="n">
         <v>1</v>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>TRNBOLXXPERXX</t>
@@ -20387,7 +19874,6 @@
       <c r="J258" t="n">
         <v>1</v>
       </c>
-      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -20406,7 +19892,6 @@
       <c r="D259" t="n">
         <v>1</v>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>TRNBOLXXPRYXX</t>
@@ -20430,7 +19915,6 @@
       <c r="J259" t="n">
         <v>1</v>
       </c>
-      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -20449,7 +19933,6 @@
       <c r="D260" t="n">
         <v>1</v>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>TRNBOLXXPRYXX</t>
@@ -20473,7 +19956,6 @@
       <c r="J260" t="n">
         <v>1</v>
       </c>
-      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -20492,7 +19974,6 @@
       <c r="D261" t="n">
         <v>1</v>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>TRNBRAXXCOLXX</t>
@@ -20516,7 +19997,6 @@
       <c r="J261" t="n">
         <v>1</v>
       </c>
-      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -20535,7 +20015,6 @@
       <c r="D262" t="n">
         <v>1</v>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>TRNBRAXXCOLXX</t>
@@ -20559,7 +20038,6 @@
       <c r="J262" t="n">
         <v>1</v>
       </c>
-      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -20578,7 +20056,6 @@
       <c r="D263" t="n">
         <v>1</v>
       </c>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>TRNBRAXXPERXX</t>
@@ -20602,7 +20079,6 @@
       <c r="J263" t="n">
         <v>1</v>
       </c>
-      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -20621,7 +20097,6 @@
       <c r="D264" t="n">
         <v>1</v>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>TRNBRAXXPERXX</t>
@@ -20645,7 +20120,6 @@
       <c r="J264" t="n">
         <v>1</v>
       </c>
-      <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -20664,7 +20138,6 @@
       <c r="D265" t="n">
         <v>1</v>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>TRNBRAXXPRYXX</t>
@@ -20688,7 +20161,6 @@
       <c r="J265" t="n">
         <v>1</v>
       </c>
-      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -20707,7 +20179,6 @@
       <c r="D266" t="n">
         <v>1</v>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>TRNBRAXXPRYXX</t>
@@ -20731,7 +20202,6 @@
       <c r="J266" t="n">
         <v>1</v>
       </c>
-      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -20750,7 +20220,6 @@
       <c r="D267" t="n">
         <v>1</v>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>TRNBRAXXURYXX</t>
@@ -20774,7 +20243,6 @@
       <c r="J267" t="n">
         <v>1</v>
       </c>
-      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -20793,7 +20261,6 @@
       <c r="D268" t="n">
         <v>1</v>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>TRNBRAXXURYXX</t>
@@ -20817,7 +20284,6 @@
       <c r="J268" t="n">
         <v>1</v>
       </c>
-      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -20836,7 +20302,6 @@
       <c r="D269" t="n">
         <v>1</v>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>TRNCHLXXPERXX</t>
@@ -20860,7 +20325,6 @@
       <c r="J269" t="n">
         <v>1</v>
       </c>
-      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -20879,7 +20343,6 @@
       <c r="D270" t="n">
         <v>1</v>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>TRNCHLXXPERXX</t>
@@ -20903,7 +20366,6 @@
       <c r="J270" t="n">
         <v>1</v>
       </c>
-      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -20922,7 +20384,6 @@
       <c r="D271" t="n">
         <v>1</v>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>TRNCOLXXECUXX</t>
@@ -20946,7 +20407,6 @@
       <c r="J271" t="n">
         <v>1</v>
       </c>
-      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -20965,7 +20425,6 @@
       <c r="D272" t="n">
         <v>1</v>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>TRNCOLXXECUXX</t>
@@ -20989,7 +20448,6 @@
       <c r="J272" t="n">
         <v>1</v>
       </c>
-      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -21008,7 +20466,6 @@
       <c r="D273" t="n">
         <v>1</v>
       </c>
-      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>TRNCOLXXPANXX</t>
@@ -21032,7 +20489,6 @@
       <c r="J273" t="n">
         <v>1</v>
       </c>
-      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -21051,7 +20507,6 @@
       <c r="D274" t="n">
         <v>1</v>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>TRNCOLXXPANXX</t>
@@ -21075,7 +20530,6 @@
       <c r="J274" t="n">
         <v>1</v>
       </c>
-      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -21094,7 +20548,6 @@
       <c r="D275" t="n">
         <v>1</v>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>TRNCOLXXPERXX</t>
@@ -21118,7 +20571,6 @@
       <c r="J275" t="n">
         <v>1</v>
       </c>
-      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -21137,7 +20589,6 @@
       <c r="D276" t="n">
         <v>1</v>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>TRNCOLXXPERXX</t>
@@ -21161,7 +20612,6 @@
       <c r="J276" t="n">
         <v>1</v>
       </c>
-      <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -21180,7 +20630,6 @@
       <c r="D277" t="n">
         <v>1</v>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>TRNCRIXXNICXX</t>
@@ -21204,7 +20653,6 @@
       <c r="J277" t="n">
         <v>1</v>
       </c>
-      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -21223,7 +20671,6 @@
       <c r="D278" t="n">
         <v>1</v>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>TRNCRIXXNICXX</t>
@@ -21247,7 +20694,6 @@
       <c r="J278" t="n">
         <v>1</v>
       </c>
-      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -21266,7 +20712,6 @@
       <c r="D279" t="n">
         <v>1</v>
       </c>
-      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>TRNCRIXXPANXX</t>
@@ -21290,7 +20735,6 @@
       <c r="J279" t="n">
         <v>1</v>
       </c>
-      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -21309,7 +20753,6 @@
       <c r="D280" t="n">
         <v>1</v>
       </c>
-      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>TRNCRIXXPANXX</t>
@@ -21333,7 +20776,6 @@
       <c r="J280" t="n">
         <v>1</v>
       </c>
-      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -21352,7 +20794,6 @@
       <c r="D281" t="n">
         <v>1</v>
       </c>
-      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>TRNDOMXXHTIXX</t>
@@ -21376,7 +20817,6 @@
       <c r="J281" t="n">
         <v>1</v>
       </c>
-      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -21395,7 +20835,6 @@
       <c r="D282" t="n">
         <v>1</v>
       </c>
-      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>TRNDOMXXHTIXX</t>
@@ -21419,7 +20858,6 @@
       <c r="J282" t="n">
         <v>1</v>
       </c>
-      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -21438,7 +20876,6 @@
       <c r="D283" t="n">
         <v>1</v>
       </c>
-      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>TRNECUXXPERXX</t>
@@ -21462,7 +20899,6 @@
       <c r="J283" t="n">
         <v>1</v>
       </c>
-      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -21481,7 +20917,6 @@
       <c r="D284" t="n">
         <v>1</v>
       </c>
-      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>TRNECUXXPERXX</t>
@@ -21505,7 +20940,6 @@
       <c r="J284" t="n">
         <v>1</v>
       </c>
-      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -21524,7 +20958,6 @@
       <c r="D285" t="n">
         <v>1</v>
       </c>
-      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>TRNGTMXXHNDXX</t>
@@ -21548,7 +20981,6 @@
       <c r="J285" t="n">
         <v>1</v>
       </c>
-      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -21567,7 +20999,6 @@
       <c r="D286" t="n">
         <v>1</v>
       </c>
-      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>TRNGTMXXHNDXX</t>
@@ -21591,7 +21022,6 @@
       <c r="J286" t="n">
         <v>1</v>
       </c>
-      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -21610,7 +21040,6 @@
       <c r="D287" t="n">
         <v>1</v>
       </c>
-      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>TRNGTMXXMEXXX</t>
@@ -21634,7 +21063,6 @@
       <c r="J287" t="n">
         <v>1</v>
       </c>
-      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -21653,7 +21081,6 @@
       <c r="D288" t="n">
         <v>1</v>
       </c>
-      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>TRNGTMXXMEXXX</t>
@@ -21677,7 +21104,6 @@
       <c r="J288" t="n">
         <v>1</v>
       </c>
-      <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -21696,7 +21122,6 @@
       <c r="D289" t="n">
         <v>1</v>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>TRNGTMXXSLVXX</t>
@@ -21720,7 +21145,6 @@
       <c r="J289" t="n">
         <v>1</v>
       </c>
-      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -21739,7 +21163,6 @@
       <c r="D290" t="n">
         <v>1</v>
       </c>
-      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>TRNGTMXXSLVXX</t>
@@ -21763,7 +21186,6 @@
       <c r="J290" t="n">
         <v>1</v>
       </c>
-      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -21782,7 +21204,6 @@
       <c r="D291" t="n">
         <v>1</v>
       </c>
-      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
           <t>TRNHNDXXNICXX</t>
@@ -21806,7 +21227,6 @@
       <c r="J291" t="n">
         <v>1</v>
       </c>
-      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -21825,7 +21245,6 @@
       <c r="D292" t="n">
         <v>1</v>
       </c>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>TRNHNDXXNICXX</t>
@@ -21849,7 +21268,6 @@
       <c r="J292" t="n">
         <v>1</v>
       </c>
-      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -21868,7 +21286,6 @@
       <c r="D293" t="n">
         <v>1</v>
       </c>
-      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>TRNHNDXXSLVXX</t>
@@ -21892,7 +21309,6 @@
       <c r="J293" t="n">
         <v>1</v>
       </c>
-      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -21911,7 +21327,6 @@
       <c r="D294" t="n">
         <v>1</v>
       </c>
-      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>TRNHNDXXSLVXX</t>
@@ -21935,16 +21350,11 @@
       <c r="J294" t="n">
         <v>1</v>
       </c>
-      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
         <v>2</v>
       </c>
-      <c r="B295" t="inlineStr"/>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>PWRLDSARGXX</t>
@@ -21968,16 +21378,11 @@
       <c r="J295" t="n">
         <v>1</v>
       </c>
-      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
         <v>2</v>
       </c>
-      <c r="B296" t="inlineStr"/>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>PWRLDSBOLXX</t>
@@ -22001,16 +21406,11 @@
       <c r="J296" t="n">
         <v>1</v>
       </c>
-      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
         <v>2</v>
       </c>
-      <c r="B297" t="inlineStr"/>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>PWRLDSBRAXX</t>
@@ -22034,16 +21434,11 @@
       <c r="J297" t="n">
         <v>1</v>
       </c>
-      <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
         <v>2</v>
       </c>
-      <c r="B298" t="inlineStr"/>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>PWRLDSBRBXX</t>
@@ -22067,16 +21462,11 @@
       <c r="J298" t="n">
         <v>1</v>
       </c>
-      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
         <v>2</v>
       </c>
-      <c r="B299" t="inlineStr"/>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>PWRLDSCHLXX</t>
@@ -22100,16 +21490,11 @@
       <c r="J299" t="n">
         <v>1</v>
       </c>
-      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
         <v>2</v>
       </c>
-      <c r="B300" t="inlineStr"/>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>PWRLDSCOLXX</t>
@@ -22133,16 +21518,11 @@
       <c r="J300" t="n">
         <v>1</v>
       </c>
-      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
         <v>2</v>
       </c>
-      <c r="B301" t="inlineStr"/>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>PWRLDSCRIXX</t>
@@ -22166,16 +21546,11 @@
       <c r="J301" t="n">
         <v>1</v>
       </c>
-      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
         <v>2</v>
       </c>
-      <c r="B302" t="inlineStr"/>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>PWRLDSDOMXX</t>
@@ -22199,16 +21574,11 @@
       <c r="J302" t="n">
         <v>1</v>
       </c>
-      <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
         <v>2</v>
       </c>
-      <c r="B303" t="inlineStr"/>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>PWRLDSECUXX</t>
@@ -22232,16 +21602,11 @@
       <c r="J303" t="n">
         <v>1</v>
       </c>
-      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
         <v>2</v>
       </c>
-      <c r="B304" t="inlineStr"/>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>PWRLDSGTMXX</t>
@@ -22265,16 +21630,11 @@
       <c r="J304" t="n">
         <v>1</v>
       </c>
-      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
         <v>2</v>
       </c>
-      <c r="B305" t="inlineStr"/>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>PWRLDSHNDXX</t>
@@ -22298,16 +21658,11 @@
       <c r="J305" t="n">
         <v>1</v>
       </c>
-      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
         <v>2</v>
       </c>
-      <c r="B306" t="inlineStr"/>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>PWRLDSHTIXX</t>
@@ -22331,16 +21686,11 @@
       <c r="J306" t="n">
         <v>1</v>
       </c>
-      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
         <v>2</v>
       </c>
-      <c r="B307" t="inlineStr"/>
-      <c r="C307" t="inlineStr"/>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>PWRLDSMEXXX</t>
@@ -22364,16 +21714,11 @@
       <c r="J307" t="n">
         <v>1</v>
       </c>
-      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
         <v>2</v>
       </c>
-      <c r="B308" t="inlineStr"/>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>PWRLDSNICXX</t>
@@ -22397,16 +21742,11 @@
       <c r="J308" t="n">
         <v>1</v>
       </c>
-      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
         <v>2</v>
       </c>
-      <c r="B309" t="inlineStr"/>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>PWRLDSPANXX</t>
@@ -22430,16 +21770,11 @@
       <c r="J309" t="n">
         <v>1</v>
       </c>
-      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
         <v>2</v>
       </c>
-      <c r="B310" t="inlineStr"/>
-      <c r="C310" t="inlineStr"/>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>PWRLDSPERXX</t>
@@ -22463,16 +21798,11 @@
       <c r="J310" t="n">
         <v>1</v>
       </c>
-      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
         <v>2</v>
       </c>
-      <c r="B311" t="inlineStr"/>
-      <c r="C311" t="inlineStr"/>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>PWRLDSPRYXX</t>
@@ -22496,16 +21826,11 @@
       <c r="J311" t="n">
         <v>1</v>
       </c>
-      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
         <v>2</v>
       </c>
-      <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>PWRLDSSLVXX</t>
@@ -22529,16 +21854,11 @@
       <c r="J312" t="n">
         <v>1</v>
       </c>
-      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
         <v>2</v>
       </c>
-      <c r="B313" t="inlineStr"/>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>PWRLDSURYXX</t>
@@ -22562,16 +21882,11 @@
       <c r="J313" t="n">
         <v>1</v>
       </c>
-      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
         <v>2</v>
       </c>
-      <c r="B314" t="inlineStr"/>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>PWRSDSARGXX</t>
@@ -22595,16 +21910,11 @@
       <c r="J314" t="n">
         <v>1</v>
       </c>
-      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
         <v>2</v>
       </c>
-      <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>PWRSDSBOLXX</t>
@@ -22628,16 +21938,11 @@
       <c r="J315" t="n">
         <v>1</v>
       </c>
-      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
         <v>2</v>
       </c>
-      <c r="B316" t="inlineStr"/>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>PWRSDSBRAXX</t>
@@ -22661,16 +21966,11 @@
       <c r="J316" t="n">
         <v>1</v>
       </c>
-      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
         <v>2</v>
       </c>
-      <c r="B317" t="inlineStr"/>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>PWRSDSBRBXX</t>
@@ -22694,16 +21994,11 @@
       <c r="J317" t="n">
         <v>1</v>
       </c>
-      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
         <v>2</v>
       </c>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>PWRSDSCHLXX</t>
@@ -22727,16 +22022,11 @@
       <c r="J318" t="n">
         <v>1</v>
       </c>
-      <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
         <v>2</v>
       </c>
-      <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>PWRSDSCOLXX</t>
@@ -22760,16 +22050,11 @@
       <c r="J319" t="n">
         <v>1</v>
       </c>
-      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
         <v>2</v>
       </c>
-      <c r="B320" t="inlineStr"/>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>PWRSDSCRIXX</t>
@@ -22793,16 +22078,11 @@
       <c r="J320" t="n">
         <v>1</v>
       </c>
-      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
         <v>2</v>
       </c>
-      <c r="B321" t="inlineStr"/>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>PWRSDSDOMXX</t>
@@ -22826,16 +22106,11 @@
       <c r="J321" t="n">
         <v>1</v>
       </c>
-      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
         <v>2</v>
       </c>
-      <c r="B322" t="inlineStr"/>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
           <t>PWRSDSECUXX</t>
@@ -22859,16 +22134,11 @@
       <c r="J322" t="n">
         <v>1</v>
       </c>
-      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
         <v>2</v>
       </c>
-      <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>PWRSDSGTMXX</t>
@@ -22892,16 +22162,11 @@
       <c r="J323" t="n">
         <v>1</v>
       </c>
-      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
         <v>2</v>
       </c>
-      <c r="B324" t="inlineStr"/>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>PWRSDSHNDXX</t>
@@ -22925,16 +22190,11 @@
       <c r="J324" t="n">
         <v>1</v>
       </c>
-      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
         <v>2</v>
       </c>
-      <c r="B325" t="inlineStr"/>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>PWRSDSHTIXX</t>
@@ -22958,16 +22218,11 @@
       <c r="J325" t="n">
         <v>1</v>
       </c>
-      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
         <v>2</v>
       </c>
-      <c r="B326" t="inlineStr"/>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>PWRSDSMEXXX</t>
@@ -22991,16 +22246,11 @@
       <c r="J326" t="n">
         <v>1</v>
       </c>
-      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
         <v>2</v>
       </c>
-      <c r="B327" t="inlineStr"/>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>PWRSDSNICXX</t>
@@ -23024,16 +22274,11 @@
       <c r="J327" t="n">
         <v>1</v>
       </c>
-      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
         <v>2</v>
       </c>
-      <c r="B328" t="inlineStr"/>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>PWRSDSPANXX</t>
@@ -23057,16 +22302,11 @@
       <c r="J328" t="n">
         <v>1</v>
       </c>
-      <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
         <v>2</v>
       </c>
-      <c r="B329" t="inlineStr"/>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>PWRSDSPERXX</t>
@@ -23090,16 +22330,11 @@
       <c r="J329" t="n">
         <v>1</v>
       </c>
-      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
         <v>2</v>
       </c>
-      <c r="B330" t="inlineStr"/>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
           <t>PWRSDSPRYXX</t>
@@ -23123,16 +22358,11 @@
       <c r="J330" t="n">
         <v>1</v>
       </c>
-      <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
         <v>2</v>
       </c>
-      <c r="B331" t="inlineStr"/>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
           <t>PWRSDSSLVXX</t>
@@ -23156,16 +22386,11 @@
       <c r="J331" t="n">
         <v>1</v>
       </c>
-      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
         <v>2</v>
       </c>
-      <c r="B332" t="inlineStr"/>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
           <t>PWRSDSURYXX</t>
@@ -23189,7 +22414,6 @@
       <c r="J332" t="n">
         <v>1</v>
       </c>
-      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -23208,7 +22432,6 @@
       <c r="D333" t="n">
         <v>1</v>
       </c>
-      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
           <t>PWRLDSARGXX</t>
@@ -23219,10 +22442,6 @@
           <t>Long duration storage (Power generator) Argentina, region XX</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -23241,7 +22460,6 @@
       <c r="D334" t="n">
         <v>1</v>
       </c>
-      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
           <t>PWRLDSBOLXX</t>
@@ -23252,10 +22470,6 @@
           <t>Long duration storage (Power generator) Bolivia, region XX</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -23274,7 +22488,6 @@
       <c r="D335" t="n">
         <v>1</v>
       </c>
-      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>PWRLDSBRAXX</t>
@@ -23285,10 +22498,6 @@
           <t>Long duration storage (Power generator) Brazil, region XX</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -23307,7 +22516,6 @@
       <c r="D336" t="n">
         <v>1</v>
       </c>
-      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
           <t>PWRLDSBRBXX</t>
@@ -23318,10 +22526,6 @@
           <t>Long duration storage (Power generator) Barbados, region XX</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -23340,7 +22544,6 @@
       <c r="D337" t="n">
         <v>1</v>
       </c>
-      <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
           <t>PWRLDSCHLXX</t>
@@ -23351,10 +22554,6 @@
           <t>Long duration storage (Power generator) Chile, region XX</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -23373,7 +22572,6 @@
       <c r="D338" t="n">
         <v>1</v>
       </c>
-      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>PWRLDSCOLXX</t>
@@ -23384,10 +22582,6 @@
           <t>Long duration storage (Power generator) Colombia, region XX</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -23406,7 +22600,6 @@
       <c r="D339" t="n">
         <v>1</v>
       </c>
-      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
           <t>PWRLDSCRIXX</t>
@@ -23417,10 +22610,6 @@
           <t>Long duration storage (Power generator) Costa Rica, region XX</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -23439,7 +22628,6 @@
       <c r="D340" t="n">
         <v>1</v>
       </c>
-      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>PWRLDSDOMXX</t>
@@ -23450,10 +22638,6 @@
           <t>Long duration storage (Power generator) Dominican Republic, region XX</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -23472,7 +22656,6 @@
       <c r="D341" t="n">
         <v>1</v>
       </c>
-      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
           <t>PWRLDSECUXX</t>
@@ -23483,10 +22666,6 @@
           <t>Long duration storage (Power generator) Ecuador, region XX</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -23505,7 +22684,6 @@
       <c r="D342" t="n">
         <v>1</v>
       </c>
-      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
           <t>PWRLDSGTMXX</t>
@@ -23516,10 +22694,6 @@
           <t>Long duration storage (Power generator) Guatemala, region XX</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -23538,7 +22712,6 @@
       <c r="D343" t="n">
         <v>1</v>
       </c>
-      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
           <t>PWRLDSHNDXX</t>
@@ -23549,10 +22722,6 @@
           <t>Long duration storage (Power generator) Honduras, region XX</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -23571,7 +22740,6 @@
       <c r="D344" t="n">
         <v>1</v>
       </c>
-      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
           <t>PWRLDSHTIXX</t>
@@ -23582,10 +22750,6 @@
           <t>Long duration storage (Power generator) Haiti, region XX</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -23604,7 +22768,6 @@
       <c r="D345" t="n">
         <v>1</v>
       </c>
-      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
           <t>PWRLDSMEXXX</t>
@@ -23615,10 +22778,6 @@
           <t>Long duration storage (Power generator) Mexico, region XX</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
-      <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -23637,7 +22796,6 @@
       <c r="D346" t="n">
         <v>1</v>
       </c>
-      <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
           <t>PWRLDSNICXX</t>
@@ -23648,10 +22806,6 @@
           <t>Long duration storage (Power generator) Nicaragua, region XX</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr"/>
-      <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -23670,7 +22824,6 @@
       <c r="D347" t="n">
         <v>1</v>
       </c>
-      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
           <t>PWRLDSPANXX</t>
@@ -23681,10 +22834,6 @@
           <t>Long duration storage (Power generator) Panama, region XX</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -23703,7 +22852,6 @@
       <c r="D348" t="n">
         <v>1</v>
       </c>
-      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
           <t>PWRLDSPERXX</t>
@@ -23714,10 +22862,6 @@
           <t>Long duration storage (Power generator) Peru, region XX</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -23736,7 +22880,6 @@
       <c r="D349" t="n">
         <v>1</v>
       </c>
-      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
           <t>PWRLDSPRYXX</t>
@@ -23747,10 +22890,6 @@
           <t>Long duration storage (Power generator) Paraguay, region XX</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -23769,7 +22908,6 @@
       <c r="D350" t="n">
         <v>1</v>
       </c>
-      <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
           <t>PWRLDSSLVXX</t>
@@ -23780,10 +22918,6 @@
           <t>Long duration storage (Power generator) El Salvador, region XX</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -23802,7 +22936,6 @@
       <c r="D351" t="n">
         <v>1</v>
       </c>
-      <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
           <t>PWRLDSURYXX</t>
@@ -23813,10 +22946,6 @@
           <t>Long duration storage (Power generator) Uruguay, region XX</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -23835,7 +22964,6 @@
       <c r="D352" t="n">
         <v>1</v>
       </c>
-      <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
           <t>PWRSDSARGXX</t>
@@ -23846,10 +22974,6 @@
           <t>Short duration storage (Power generator) Argentina, region XX</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -23868,7 +22992,6 @@
       <c r="D353" t="n">
         <v>1</v>
       </c>
-      <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
           <t>PWRSDSBOLXX</t>
@@ -23879,10 +23002,6 @@
           <t>Short duration storage (Power generator) Bolivia, region XX</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -23901,7 +23020,6 @@
       <c r="D354" t="n">
         <v>1</v>
       </c>
-      <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
           <t>PWRSDSBRAXX</t>
@@ -23912,10 +23030,6 @@
           <t>Short duration storage (Power generator) Brazil, region XX</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
-      <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -23934,7 +23048,6 @@
       <c r="D355" t="n">
         <v>1</v>
       </c>
-      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
           <t>PWRSDSBRBXX</t>
@@ -23945,10 +23058,6 @@
           <t>Short duration storage (Power generator) Barbados, region XX</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -23967,7 +23076,6 @@
       <c r="D356" t="n">
         <v>1</v>
       </c>
-      <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
           <t>PWRSDSCHLXX</t>
@@ -23978,10 +23086,6 @@
           <t>Short duration storage (Power generator) Chile, region XX</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -24000,7 +23104,6 @@
       <c r="D357" t="n">
         <v>1</v>
       </c>
-      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>PWRSDSCOLXX</t>
@@ -24011,10 +23114,6 @@
           <t>Short duration storage (Power generator) Colombia, region XX</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
-      <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -24033,7 +23132,6 @@
       <c r="D358" t="n">
         <v>1</v>
       </c>
-      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
           <t>PWRSDSCRIXX</t>
@@ -24044,10 +23142,6 @@
           <t>Short duration storage (Power generator) Costa Rica, region XX</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -24066,7 +23160,6 @@
       <c r="D359" t="n">
         <v>1</v>
       </c>
-      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
           <t>PWRSDSDOMXX</t>
@@ -24077,10 +23170,6 @@
           <t>Short duration storage (Power generator) Dominican Republic, region XX</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -24099,7 +23188,6 @@
       <c r="D360" t="n">
         <v>1</v>
       </c>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>PWRSDSECUXX</t>
@@ -24110,10 +23198,6 @@
           <t>Short duration storage (Power generator) Ecuador, region XX</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -24132,7 +23216,6 @@
       <c r="D361" t="n">
         <v>1</v>
       </c>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
           <t>PWRSDSGTMXX</t>
@@ -24143,10 +23226,6 @@
           <t>Short duration storage (Power generator) Guatemala, region XX</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -24165,7 +23244,6 @@
       <c r="D362" t="n">
         <v>1</v>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>PWRSDSHNDXX</t>
@@ -24176,10 +23254,6 @@
           <t>Short duration storage (Power generator) Honduras, region XX</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -24198,7 +23272,6 @@
       <c r="D363" t="n">
         <v>1</v>
       </c>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>PWRSDSHTIXX</t>
@@ -24209,10 +23282,6 @@
           <t>Short duration storage (Power generator) Haiti, region XX</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
-      <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -24231,7 +23300,6 @@
       <c r="D364" t="n">
         <v>1</v>
       </c>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
           <t>PWRSDSMEXXX</t>
@@ -24242,10 +23310,6 @@
           <t>Short duration storage (Power generator) Mexico, region XX</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -24264,7 +23328,6 @@
       <c r="D365" t="n">
         <v>1</v>
       </c>
-      <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
           <t>PWRSDSNICXX</t>
@@ -24275,10 +23338,6 @@
           <t>Short duration storage (Power generator) Nicaragua, region XX</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -24297,7 +23356,6 @@
       <c r="D366" t="n">
         <v>1</v>
       </c>
-      <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
           <t>PWRSDSPANXX</t>
@@ -24308,10 +23366,6 @@
           <t>Short duration storage (Power generator) Panama, region XX</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -24330,7 +23384,6 @@
       <c r="D367" t="n">
         <v>1</v>
       </c>
-      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>PWRSDSPERXX</t>
@@ -24341,10 +23394,6 @@
           <t>Short duration storage (Power generator) Peru, region XX</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -24363,7 +23412,6 @@
       <c r="D368" t="n">
         <v>1</v>
       </c>
-      <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
           <t>PWRSDSPRYXX</t>
@@ -24374,10 +23422,6 @@
           <t>Short duration storage (Power generator) Paraguay, region XX</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -24396,7 +23440,6 @@
       <c r="D369" t="n">
         <v>1</v>
       </c>
-      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
           <t>PWRSDSSLVXX</t>
@@ -24407,10 +23450,6 @@
           <t>Short duration storage (Power generator) El Salvador, region XX</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -24429,7 +23468,6 @@
       <c r="D370" t="n">
         <v>1</v>
       </c>
-      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
           <t>PWRSDSURYXX</t>
@@ -24440,10 +23478,6 @@
           <t>Short duration storage (Power generator) Uruguay, region XX</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
-      <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24544,7 +23578,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>RNWTRNBRBXX</t>
@@ -24568,7 +23601,6 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -24587,7 +23619,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>RNWRPOBRBXX</t>
@@ -24611,7 +23642,6 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -24630,7 +23660,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>RNWNLIBRBXX</t>
@@ -24654,7 +23683,6 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -24673,7 +23701,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRTRNBRBXX</t>
@@ -24697,7 +23724,6 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -24716,7 +23742,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TRNRPOBRBXX</t>
@@ -24740,7 +23765,6 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -24759,7 +23783,6 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TRNNLIBRBXX</t>
@@ -24783,7 +23806,6 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -24802,7 +23824,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>DSPTRNBRBXX</t>
@@ -24826,7 +23847,6 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -24845,7 +23865,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>DSPTRNBRBXX</t>
@@ -24869,7 +23888,6 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -24888,7 +23906,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>RNWTRNBOLXX</t>
@@ -24912,7 +23929,6 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -24931,7 +23947,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>RNWRPOBOLXX</t>
@@ -24955,7 +23970,6 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -24974,7 +23988,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>RNWNLIBOLXX</t>
@@ -24998,7 +24011,6 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -25017,7 +24029,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRTRNBOLXX</t>
@@ -25041,7 +24052,6 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -25060,7 +24070,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>TRNRPOBOLXX</t>
@@ -25084,7 +24093,6 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -25103,7 +24111,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>TRNNLIBOLXX</t>
@@ -25127,7 +24134,6 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -25146,7 +24152,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>DSPTRNBOLXX</t>
@@ -25170,7 +24175,6 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -25189,7 +24193,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>DSPTRNBOLXX</t>
@@ -25213,7 +24216,6 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -25232,7 +24234,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>RNWTRNCHLXX</t>
@@ -25256,7 +24257,6 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -25275,7 +24275,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>RNWRPOCHLXX</t>
@@ -25299,7 +24298,6 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -25318,7 +24316,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>RNWNLICHLXX</t>
@@ -25342,7 +24339,6 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -25361,7 +24357,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRTRNCHLXX</t>
@@ -25385,7 +24380,6 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -25404,7 +24398,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>TRNRPOCHLXX</t>
@@ -25428,7 +24421,6 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -25447,7 +24439,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>TRNNLICHLXX</t>
@@ -25471,7 +24462,6 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -25490,7 +24480,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>DSPTRNCHLXX</t>
@@ -25514,7 +24503,6 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -25533,7 +24521,6 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>DSPTRNCHLXX</t>
@@ -25557,7 +24544,6 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -25576,7 +24562,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>RNWTRNCOLXX</t>
@@ -25600,7 +24585,6 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -25619,7 +24603,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>RNWRPOCOLXX</t>
@@ -25643,7 +24626,6 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -25662,7 +24644,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>RNWNLICOLXX</t>
@@ -25686,7 +24667,6 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -25705,7 +24685,6 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRTRNCOLXX</t>
@@ -25729,7 +24708,6 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -25748,7 +24726,6 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>TRNRPOCOLXX</t>
@@ -25772,7 +24749,6 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -25791,7 +24767,6 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>TRNNLICOLXX</t>
@@ -25815,7 +24790,6 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -25834,7 +24808,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>DSPTRNCOLXX</t>
@@ -25858,7 +24831,6 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -25877,7 +24849,6 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>DSPTRNCOLXX</t>
@@ -25901,7 +24872,6 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -25920,7 +24890,6 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>RNWTRNCRIXX</t>
@@ -25944,7 +24913,6 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -25963,7 +24931,6 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>RNWRPOCRIXX</t>
@@ -25987,7 +24954,6 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -26006,7 +24972,6 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>RNWNLICRIXX</t>
@@ -26030,7 +24995,6 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -26049,7 +25013,6 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRTRNCRIXX</t>
@@ -26073,7 +25036,6 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -26092,7 +25054,6 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>TRNRPOCRIXX</t>
@@ -26116,7 +25077,6 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -26135,7 +25095,6 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>TRNNLICRIXX</t>
@@ -26159,7 +25118,6 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -26178,7 +25136,6 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>DSPTRNCRIXX</t>
@@ -26202,7 +25159,6 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -26221,7 +25177,6 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>DSPTRNCRIXX</t>
@@ -26245,7 +25200,6 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -26264,7 +25218,6 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>RNWTRNECUXX</t>
@@ -26288,7 +25241,6 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -26307,7 +25259,6 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>RNWRPOECUXX</t>
@@ -26331,7 +25282,6 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -26350,7 +25300,6 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>RNWNLIECUXX</t>
@@ -26374,7 +25323,6 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -26393,7 +25341,6 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRTRNECUXX</t>
@@ -26417,7 +25364,6 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -26436,7 +25382,6 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>TRNRPOECUXX</t>
@@ -26460,7 +25405,6 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -26479,7 +25423,6 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>TRNNLIECUXX</t>
@@ -26503,7 +25446,6 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -26522,7 +25464,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>DSPTRNECUXX</t>
@@ -26546,7 +25487,6 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -26565,7 +25505,6 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>DSPTRNECUXX</t>
@@ -26589,7 +25528,6 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -26608,7 +25546,6 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>RNWTRNSLVXX</t>
@@ -26632,7 +25569,6 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -26651,7 +25587,6 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>RNWRPOSLVXX</t>
@@ -26675,7 +25610,6 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -26694,7 +25628,6 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>RNWNLISLVXX</t>
@@ -26718,7 +25651,6 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -26737,7 +25669,6 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRTRNSLVXX</t>
@@ -26761,7 +25692,6 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -26780,7 +25710,6 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>TRNRPOSLVXX</t>
@@ -26804,7 +25733,6 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -26823,7 +25751,6 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>TRNNLISLVXX</t>
@@ -26847,7 +25774,6 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -26866,7 +25792,6 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>DSPTRNSLVXX</t>
@@ -26890,7 +25815,6 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -26909,7 +25833,6 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>DSPTRNSLVXX</t>
@@ -26933,7 +25856,6 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -26952,7 +25874,6 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>RNWTRNGTMXX</t>
@@ -26976,7 +25897,6 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -26995,7 +25915,6 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>RNWRPOGTMXX</t>
@@ -27019,7 +25938,6 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -27038,7 +25956,6 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>RNWNLIGTMXX</t>
@@ -27062,7 +25979,6 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -27081,7 +25997,6 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRTRNGTMXX</t>
@@ -27105,7 +26020,6 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -27124,7 +26038,6 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>TRNRPOGTMXX</t>
@@ -27148,7 +26061,6 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -27167,7 +26079,6 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>TRNNLIGTMXX</t>
@@ -27191,7 +26102,6 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -27210,7 +26120,6 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>DSPTRNGTMXX</t>
@@ -27234,7 +26143,6 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -27253,7 +26161,6 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>DSPTRNGTMXX</t>
@@ -27277,7 +26184,6 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -27296,7 +26202,6 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>RNWTRNHTIXX</t>
@@ -27320,7 +26225,6 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -27339,7 +26243,6 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>RNWRPOHTIXX</t>
@@ -27363,7 +26266,6 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -27382,7 +26284,6 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>RNWNLIHTIXX</t>
@@ -27406,7 +26307,6 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -27425,7 +26325,6 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRTRNHTIXX</t>
@@ -27449,7 +26348,6 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -27468,7 +26366,6 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>TRNRPOHTIXX</t>
@@ -27492,7 +26389,6 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -27511,7 +26407,6 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>TRNNLIHTIXX</t>
@@ -27535,7 +26430,6 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -27554,7 +26448,6 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>DSPTRNHTIXX</t>
@@ -27578,7 +26471,6 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -27597,7 +26489,6 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>DSPTRNHTIXX</t>
@@ -27621,7 +26512,6 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -27640,7 +26530,6 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>RNWTRNHNDXX</t>
@@ -27664,7 +26553,6 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -27683,7 +26571,6 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>RNWRPOHNDXX</t>
@@ -27707,7 +26594,6 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -27726,7 +26612,6 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>RNWNLIHNDXX</t>
@@ -27750,7 +26635,6 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -27769,7 +26653,6 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWRTRNHNDXX</t>
@@ -27793,7 +26676,6 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -27812,7 +26694,6 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>TRNRPOHNDXX</t>
@@ -27836,7 +26717,6 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -27855,7 +26735,6 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>TRNNLIHNDXX</t>
@@ -27879,7 +26758,6 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -27898,7 +26776,6 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>DSPTRNHNDXX</t>
@@ -27922,7 +26799,6 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -27941,7 +26817,6 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>DSPTRNHNDXX</t>
@@ -27965,7 +26840,6 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -27984,7 +26858,6 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>RNWTRNNICXX</t>
@@ -28008,7 +26881,6 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -28027,7 +26899,6 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>RNWRPONICXX</t>
@@ -28051,7 +26922,6 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -28070,7 +26940,6 @@
       <c r="D84" t="n">
         <v>1</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>RNWNLINICXX</t>
@@ -28094,7 +26963,6 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -28113,7 +26981,6 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>PWRTRNNICXX</t>
@@ -28137,7 +27004,6 @@
       <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -28156,7 +27022,6 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>TRNRPONICXX</t>
@@ -28180,7 +27045,6 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -28199,7 +27063,6 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>TRNNLINICXX</t>
@@ -28223,7 +27086,6 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -28242,7 +27104,6 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>DSPTRNNICXX</t>
@@ -28266,7 +27127,6 @@
       <c r="J88" t="n">
         <v>1</v>
       </c>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -28285,7 +27145,6 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>DSPTRNNICXX</t>
@@ -28309,7 +27168,6 @@
       <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -28328,7 +27186,6 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>RNWTRNPANXX</t>
@@ -28352,7 +27209,6 @@
       <c r="J90" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -28371,7 +27227,6 @@
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>RNWRPOPANXX</t>
@@ -28395,7 +27250,6 @@
       <c r="J91" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -28414,7 +27268,6 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>RNWNLIPANXX</t>
@@ -28438,7 +27291,6 @@
       <c r="J92" t="n">
         <v>1</v>
       </c>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -28457,7 +27309,6 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>PWRTRNPANXX</t>
@@ -28481,7 +27332,6 @@
       <c r="J93" t="n">
         <v>1</v>
       </c>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -28500,7 +27350,6 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>TRNRPOPANXX</t>
@@ -28524,7 +27373,6 @@
       <c r="J94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -28543,7 +27391,6 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>TRNNLIPANXX</t>
@@ -28567,7 +27414,6 @@
       <c r="J95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -28586,7 +27432,6 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>DSPTRNPANXX</t>
@@ -28610,7 +27455,6 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
-      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -28629,7 +27473,6 @@
       <c r="D97" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>DSPTRNPANXX</t>
@@ -28653,7 +27496,6 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -28672,7 +27514,6 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>RNWTRNPRYXX</t>
@@ -28696,7 +27537,6 @@
       <c r="J98" t="n">
         <v>1</v>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -28715,7 +27555,6 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>RNWRPOPRYXX</t>
@@ -28739,7 +27578,6 @@
       <c r="J99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -28758,7 +27596,6 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>RNWNLIPRYXX</t>
@@ -28782,7 +27619,6 @@
       <c r="J100" t="n">
         <v>1</v>
       </c>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -28801,7 +27637,6 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>PWRTRNPRYXX</t>
@@ -28825,7 +27660,6 @@
       <c r="J101" t="n">
         <v>1</v>
       </c>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -28844,7 +27678,6 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>TRNRPOPRYXX</t>
@@ -28868,7 +27701,6 @@
       <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -28887,7 +27719,6 @@
       <c r="D103" t="n">
         <v>1</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>TRNNLIPRYXX</t>
@@ -28911,7 +27742,6 @@
       <c r="J103" t="n">
         <v>1</v>
       </c>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -28930,7 +27760,6 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>DSPTRNPRYXX</t>
@@ -28954,7 +27783,6 @@
       <c r="J104" t="n">
         <v>1</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -28973,7 +27801,6 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>DSPTRNPRYXX</t>
@@ -28997,7 +27824,6 @@
       <c r="J105" t="n">
         <v>1</v>
       </c>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -29016,7 +27842,6 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>RNWTRNPERXX</t>
@@ -29040,7 +27865,6 @@
       <c r="J106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -29059,7 +27883,6 @@
       <c r="D107" t="n">
         <v>1</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>RNWRPOPERXX</t>
@@ -29083,7 +27906,6 @@
       <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -29102,7 +27924,6 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>RNWNLIPERXX</t>
@@ -29126,7 +27947,6 @@
       <c r="J108" t="n">
         <v>1</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -29145,7 +27965,6 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>PWRTRNPERXX</t>
@@ -29169,7 +27988,6 @@
       <c r="J109" t="n">
         <v>1</v>
       </c>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -29188,7 +28006,6 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>TRNRPOPERXX</t>
@@ -29212,7 +28029,6 @@
       <c r="J110" t="n">
         <v>1</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -29231,7 +28047,6 @@
       <c r="D111" t="n">
         <v>1</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>TRNNLIPERXX</t>
@@ -29255,7 +28070,6 @@
       <c r="J111" t="n">
         <v>1</v>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -29274,7 +28088,6 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>DSPTRNPERXX</t>
@@ -29298,7 +28111,6 @@
       <c r="J112" t="n">
         <v>1</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -29317,7 +28129,6 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>DSPTRNPERXX</t>
@@ -29341,7 +28152,6 @@
       <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -29360,7 +28170,6 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>RNWTRNDOMXX</t>
@@ -29384,7 +28193,6 @@
       <c r="J114" t="n">
         <v>1</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -29403,7 +28211,6 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>RNWRPODOMXX</t>
@@ -29427,7 +28234,6 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -29446,7 +28252,6 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>RNWNLIDOMXX</t>
@@ -29470,7 +28275,6 @@
       <c r="J116" t="n">
         <v>1</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -29489,7 +28293,6 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>PWRTRNDOMXX</t>
@@ -29513,7 +28316,6 @@
       <c r="J117" t="n">
         <v>1</v>
       </c>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -29532,7 +28334,6 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>TRNRPODOMXX</t>
@@ -29556,7 +28357,6 @@
       <c r="J118" t="n">
         <v>1</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -29575,7 +28375,6 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>TRNNLIDOMXX</t>
@@ -29599,7 +28398,6 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -29618,7 +28416,6 @@
       <c r="D120" t="n">
         <v>1</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>DSPTRNDOMXX</t>
@@ -29642,7 +28439,6 @@
       <c r="J120" t="n">
         <v>1</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -29661,7 +28457,6 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>DSPTRNDOMXX</t>
@@ -29685,7 +28480,6 @@
       <c r="J121" t="n">
         <v>1</v>
       </c>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -29704,7 +28498,6 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>RNWTRNURYXX</t>
@@ -29728,7 +28521,6 @@
       <c r="J122" t="n">
         <v>1</v>
       </c>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -29747,7 +28539,6 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>RNWRPOURYXX</t>
@@ -29771,7 +28562,6 @@
       <c r="J123" t="n">
         <v>1</v>
       </c>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -29790,7 +28580,6 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>RNWNLIURYXX</t>
@@ -29814,7 +28603,6 @@
       <c r="J124" t="n">
         <v>1</v>
       </c>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -29833,7 +28621,6 @@
       <c r="D125" t="n">
         <v>1</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>PWRTRNURYXX</t>
@@ -29857,7 +28644,6 @@
       <c r="J125" t="n">
         <v>1</v>
       </c>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -29876,7 +28662,6 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>TRNRPOURYXX</t>
@@ -29900,7 +28685,6 @@
       <c r="J126" t="n">
         <v>1</v>
       </c>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -29919,7 +28703,6 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>TRNNLIURYXX</t>
@@ -29943,7 +28726,6 @@
       <c r="J127" t="n">
         <v>1</v>
       </c>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -29962,7 +28744,6 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>DSPTRNURYXX</t>
@@ -29986,7 +28767,6 @@
       <c r="J128" t="n">
         <v>1</v>
       </c>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -30005,7 +28785,6 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>DSPTRNURYXX</t>
@@ -30029,7 +28808,6 @@
       <c r="J129" t="n">
         <v>1</v>
       </c>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -30048,7 +28826,6 @@
       <c r="D130" t="n">
         <v>1</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>RNWTRNBRAXX</t>
@@ -30072,7 +28849,6 @@
       <c r="J130" t="n">
         <v>1</v>
       </c>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -30091,7 +28867,6 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>RNWRPOBRAXX</t>
@@ -30115,7 +28890,6 @@
       <c r="J131" t="n">
         <v>1</v>
       </c>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -30134,7 +28908,6 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>RNWNLIBRAXX</t>
@@ -30158,7 +28931,6 @@
       <c r="J132" t="n">
         <v>1</v>
       </c>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -30177,7 +28949,6 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>PWRTRNBRAXX</t>
@@ -30201,7 +28972,6 @@
       <c r="J133" t="n">
         <v>1</v>
       </c>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -30220,7 +28990,6 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>TRNRPOBRAXX</t>
@@ -30244,7 +29013,6 @@
       <c r="J134" t="n">
         <v>1</v>
       </c>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -30263,7 +29031,6 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>TRNNLIBRAXX</t>
@@ -30287,7 +29054,6 @@
       <c r="J135" t="n">
         <v>1</v>
       </c>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -30306,7 +29072,6 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>DSPTRNBRAXX</t>
@@ -30330,7 +29095,6 @@
       <c r="J136" t="n">
         <v>1</v>
       </c>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -30349,7 +29113,6 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>DSPTRNBRAXX</t>
@@ -30373,7 +29136,6 @@
       <c r="J137" t="n">
         <v>1</v>
       </c>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -30392,7 +29154,6 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>RNWTRNMEXXX</t>
@@ -30416,7 +29177,6 @@
       <c r="J138" t="n">
         <v>1</v>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -30435,7 +29195,6 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>RNWRPOMEXXX</t>
@@ -30459,7 +29218,6 @@
       <c r="J139" t="n">
         <v>1</v>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -30478,7 +29236,6 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>RNWNLIMEXXX</t>
@@ -30502,7 +29259,6 @@
       <c r="J140" t="n">
         <v>1</v>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -30521,7 +29277,6 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>PWRTRNMEXXX</t>
@@ -30545,7 +29300,6 @@
       <c r="J141" t="n">
         <v>1</v>
       </c>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -30564,7 +29318,6 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>TRNRPOMEXXX</t>
@@ -30588,7 +29341,6 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -30607,7 +29359,6 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>TRNNLIMEXXX</t>
@@ -30631,7 +29382,6 @@
       <c r="J143" t="n">
         <v>1</v>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -30650,7 +29400,6 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>DSPTRNMEXXX</t>
@@ -30674,7 +29423,6 @@
       <c r="J144" t="n">
         <v>1</v>
       </c>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -30693,7 +29441,6 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>DSPTRNMEXXX</t>
@@ -30717,7 +29464,6 @@
       <c r="J145" t="n">
         <v>1</v>
       </c>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -30736,7 +29482,6 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>RNWTRNARGXX</t>
@@ -30760,7 +29505,6 @@
       <c r="J146" t="n">
         <v>1</v>
       </c>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -30779,7 +29523,6 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>RNWRPOARGXX</t>
@@ -30803,7 +29546,6 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -30822,7 +29564,6 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>RNWNLIARGXX</t>
@@ -30846,7 +29587,6 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -30865,7 +29605,6 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>PWRTRNARGXX</t>
@@ -30889,7 +29628,6 @@
       <c r="J149" t="n">
         <v>1</v>
       </c>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -30908,7 +29646,6 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>TRNRPOARGXX</t>
@@ -30932,7 +29669,6 @@
       <c r="J150" t="n">
         <v>1</v>
       </c>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -30951,7 +29687,6 @@
       <c r="D151" t="n">
         <v>1</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>TRNNLIARGXX</t>
@@ -30975,7 +29710,6 @@
       <c r="J151" t="n">
         <v>1</v>
       </c>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -30994,7 +29728,6 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>DSPTRNARGXX</t>
@@ -31018,7 +29751,6 @@
       <c r="J152" t="n">
         <v>1</v>
       </c>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -31037,7 +29769,6 @@
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>DSPTRNARGXX</t>
@@ -31061,7 +29792,6 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
-      <c r="K153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
